--- a/output/pdf_financials_xlsx/CELL.xlsx
+++ b/output/pdf_financials_xlsx/CELL.xlsx
@@ -4439,40 +4439,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.078226</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.085453</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.994446</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.118648</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.118648</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.193958</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.193958</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.566124</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.566124</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.125879</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.125879</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.125879</v>
       </c>
     </row>
     <row r="93">
@@ -7296,7 +7296,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -8604,7 +8608,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -9186,7 +9194,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -9872,7 +9884,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -10404,7 +10420,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>0.078226</v>
       </c>

--- a/output/pdf_financials_xlsx/CELL.xlsx
+++ b/output/pdf_financials_xlsx/CELL.xlsx
@@ -879,22 +879,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002827</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>2.9e-05</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>3.2e-05</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.051197</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.104653</v>
       </c>
     </row>
     <row r="13">
@@ -1580,22 +1580,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.246027</v>
+        <v>-0.248854</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.420304</v>
+        <v>-0.420308</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-4.369797</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.630044</v>
+        <v>-0.630073</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.461385</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.8045020000000001</v>
+        <v>-0.804534</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.759467</v>
@@ -1610,10 +1610,10 @@
         <v>1.16885</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.365818</v>
+        <v>-1.417015</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.888561</v>
+        <v>-3.993214</v>
       </c>
     </row>
     <row r="28">
@@ -1666,22 +1666,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.246027</v>
+        <v>-0.248854</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.420304</v>
+        <v>-0.420308</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-4.369797</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.630044</v>
+        <v>-0.630073</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0.461385</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.8045020000000001</v>
+        <v>-0.804534</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.737767</v>
@@ -1696,10 +1696,10 @@
         <v>1.17594</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.355182</v>
+        <v>-1.406379</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.877925</v>
+        <v>-3.982578</v>
       </c>
     </row>
     <row r="30">
@@ -1908,25 +1908,25 @@
         <v>1.328995</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.063313</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.409303</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.301655</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.502109</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.246147</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>6.067899</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.17348</v>
       </c>
     </row>
     <row r="35">
@@ -1994,25 +1994,25 @@
         <v>1.328995</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.063313</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.409303</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.301655</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.25</v>
+        <v>0.752109</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>3</v>
+        <v>7.246147</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>6.067899</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.17348</v>
       </c>
     </row>
     <row r="37">
@@ -2510,25 +2510,25 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.080619</v>
+        <v>0.017306</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.425008</v>
+        <v>0.015705</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.305056</v>
+        <v>0.003401</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.525056</v>
+        <v>0.022947</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.298085</v>
+        <v>0.051938</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>6.145359</v>
+        <v>0.07746</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.405864</v>
+        <v>0.232384</v>
       </c>
     </row>
     <row r="49">
@@ -5808,19 +5808,19 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.023408</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.021859</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="125">
@@ -5851,19 +5851,19 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.023408</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.021859</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="126">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -11798,7 +11798,11 @@
           <t>Lease payments 14</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -14620,7 +14624,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -21354,7 +21362,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -27872,7 +27880,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E291" s="5" t="n">

--- a/output/pdf_financials_xlsx/CELL.xlsx
+++ b/output/pdf_financials_xlsx/CELL.xlsx
@@ -3336,40 +3336,40 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0065</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.116006</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="68">
@@ -3379,40 +3379,40 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.008279</v>
+        <v>0.014779</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.046981</v>
+        <v>0.061981</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.047351</v>
+        <v>0.057351</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.026197</v>
+        <v>0.051197</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.025464</v>
+        <v>0.050464</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.123187</v>
+        <v>0.239193</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.078308</v>
+        <v>0.152308</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.03402</v>
+        <v>0.05402</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.021483</v>
+        <v>0.041483</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.029659</v>
+        <v>0.056659</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.126074</v>
+        <v>0.151074</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.06907000000000001</v>
+        <v>0.09407</v>
       </c>
     </row>
     <row r="69">
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.010999</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0</v>
@@ -3698,22 +3698,22 @@
         <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.02211</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.021859</v>
+        <v>0.001859</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.010336</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.011194</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.003935</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -5210,13 +5210,13 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.001558</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.001664</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.000806</v>
       </c>
     </row>
     <row r="111">
@@ -5428,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>5.026749</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -10714,7 +10714,11 @@
           <t>Accretion expense 14</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -11426,7 +11430,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -12826,7 +12834,11 @@
           <t>Accretion expense 14</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
